--- a/base_prov_co/larebaja/larebaja_abbott_2026_10_02.xlsx
+++ b/base_prov_co/larebaja/larebaja_abbott_2026_10_02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La Rebaja" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'La Rebaja'!$A$1:$Q$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'La Rebaja'!$A$1:$R$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,65 +471,70 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoría</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoración</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>url_imagen</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -556,15 +561,14 @@
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -577,34 +581,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>29</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>138</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Un vaso de Ensure® proporciona: 28 vitaminas y minerales esenciales, calcio y antioxidantes, vitamina D, omega-3 y es fuente de fibra FOS.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1977502-800-auto?v=639264347636530000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-polvo-vainilla-110478/p</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -631,15 +640,14 @@
           <t>7703186032157</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -652,34 +660,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>82</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>213</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1963745-800-auto?v=639228048937370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/oferta-ensure-advance-x-850-gr-ensure-advance-x-400-gr-137771/p</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -706,15 +719,14 @@
           <t>8710428018670</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,34 +739,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>31</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>213</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1888698-800-auto?v=639110118237630000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-rpb-vainilla-150100/p</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -781,15 +798,14 @@
           <t>7703186033031</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -802,34 +818,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>31</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>213</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890101-800-auto?v=639110363262500000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-vainilla-154574/p</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -856,15 +877,14 @@
           <t>8710428018717</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -877,34 +897,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>28</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>213</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1888710-800-auto?v=639110119017970000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-rpb-fresa-150102/p</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -931,15 +956,14 @@
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -952,34 +976,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>26</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>138</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Un vaso de Ensure® proporciona: 28 vitaminas y minerales esenciales, calcio y antioxidantes, vitamina D, omega-3 y es fuente de fibra FOS.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1977623-800-auto?v=639264359672530000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-polvo-fresa-129728/p</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1006,15 +1035,14 @@
           <t>8710428013873</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1027,34 +1055,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>26</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>213</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1978552-800-auto?v=639265232290930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-polvo-fresa-129727/p</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1071,21 +1104,19 @@
           <t>La Rebaja</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1098,8 +1129,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1110,14 +1143,15 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-rpb-chocolate-150101/p</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1144,15 +1178,14 @@
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1165,34 +1198,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>21</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>138</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Un vaso de Ensure® proporciona: 28 vitaminas y minerales esenciales, calcio y antioxidantes, vitamina D, omega-3 y es fuente de fibra FOS.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1879656-800-auto?v=639107825686130000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-polvo-vainilla-43640/p</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1219,15 +1257,14 @@
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1240,34 +1277,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>23</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>138</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Un vaso de Ensure® proporciona: 28 vitaminas y minerales esenciales, calcio y antioxidantes, vitamina D, omega-3 y es fuente de fibra FOS.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1889020-800-auto?v=639110163760630000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-vainilla-150864/p</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1294,15 +1336,14 @@
           <t>7703186031433</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1315,34 +1356,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>23</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>218</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Ensure® Clinical es nutrición especializada para adultos con HMB, proteína, 28 vitaminas, minerales y 1.5Kcal/mL. Ideal para apoyar la recuperación de la perdida severa de masa muscular debido a una condición de salud.</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1884679-800-auto?v=639109065657030000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-clinical-122506/p</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1369,15 +1415,14 @@
           <t>8710428018861</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1390,34 +1435,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>6</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>27</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>230</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Ensure® Advance es nutrición especializada para adultos con HMB, proteína y 28 vitaminas y minerales. Ideal para ayudar a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1889026-800-auto?v=639110164157330000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-cafe-150865/p</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1444,15 +1494,14 @@
           <t>7703186341334</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1465,30 +1514,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>25</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1978021-800-auto?v=639264399223130000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-cafe-polvo-157327/p</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1515,15 +1568,14 @@
           <t>8710428011848</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1536,30 +1588,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>30</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1977068-800-auto?v=639263471843030000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/ensure-advance-polvo-chocolate-132697/p</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1586,15 +1642,14 @@
           <t>7703186069917</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1607,30 +1662,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>9</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1882263-800-auto?v=639108233359700000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pulmocare-98944/p</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1657,15 +1716,14 @@
           <t>7703186030191</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1678,30 +1736,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>8</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1882548-800-auto?v=639108282117070000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/nepro-bp-103276/p</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1728,15 +1790,14 @@
           <t>7703186030184</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1749,30 +1810,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>8</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1882550-800-auto?v=639108282414030000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/nepro-ap-103277/p</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1799,15 +1864,14 @@
           <t>8427030008943</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1820,34 +1884,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>6</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>23</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>222</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>¡Controla tus niveles de azúcar! Glucerna® te ayuda a estabilizar tus niveles de azúcar desde el primer día gracias a su doble método de acción que permite mejorar la producción de insulina y reducir la resistencia a ella.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1959563-800-auto?v=639216119246670000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/alimento-glucerna-polvo-propositos-medicos-vainilla-155136/p</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1874,15 +1943,14 @@
           <t>7703186030283</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1895,34 +1963,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>6</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>25</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>222</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>¡Controla tus niveles de azúcar! Glucerna® te ayuda a estabilizar tus niveles de azúcar desde el primer día gracias a su doble método de acción que permite mejorar la producción de insulina y reducir la resistencia a ella.</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1883095-800-auto?v=639108376500000000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/glucerna-vainilla-110371/p</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1949,15 +2022,14 @@
           <t>7703186499844</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1970,34 +2042,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>82</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>213</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1963745-800-auto?v=639228048937370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/oferta-ensure-advance-x-850-gr-ensure-advance-x-400-gr-137771/p</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2024,15 +2101,14 @@
           <t>7703186032737</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2045,34 +2121,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>6</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>39</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>222</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>¡Controla tus niveles de azúcar! Glucerna® te ayuda a estabilizar tus niveles de azúcar desde el primer día gracias a su doble método de acción que permite mejorar la producción de insulina y reducir la resistencia a ella.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890112-800-auto?v=639110365112700000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/glucerna-vainilla-pack-x-6-unds-154586/p</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2099,15 +2180,14 @@
           <t>7703186190376</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2120,30 +2200,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>45</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1963831-800-auto?v=639228059000500000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/oferta-ensure-advance-liquido-dscto-20-8-un-156962/p</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2170,15 +2254,14 @@
           <t>7703186031525</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2191,34 +2274,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>6</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>22</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>222</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>¡Controla tus niveles de azúcar! Glucerna® te ayuda a estabilizar tus niveles de azúcar desde el primer día gracias a su doble método de acción que permite mejorar la producción de insulina y reducir la resistencia a ella.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1948530-800-auto?v=639190890321570000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/glucerna-fresa-115313/p</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2245,15 +2333,14 @@
           <t>7703186358035</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2266,30 +2353,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>45</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1933884-800-auto?v=639152033706530000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/oferta-glucerna-polvo-400-grs-vainilla-gratis-156956/p</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2316,15 +2407,14 @@
           <t>8427030009346</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2337,30 +2427,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>24</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1942555-800-auto?v=639167595673670000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/glucerna-capuchino-polvo-157457/p</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2387,15 +2481,14 @@
           <t>8710428024299</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2408,34 +2501,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>6</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>34</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>222</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>¡Controla tus niveles de azúcar! Glucerna® te ayuda a estabilizar tus niveles de azúcar desde el primer día gracias a su doble método de acción que permite mejorar la producción de insulina y reducir la resistencia a ella.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1891930-800-auto?v=639110906696900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/glucerna-1-6-kcal-sabor-a-vainilla-156280/p</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2462,15 +2560,14 @@
           <t>7501033957376</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2483,30 +2580,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>43</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1881928-800-auto?v=639108181165370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-de-rehidratacion-pedialyte-max-60-uva-91342/p</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2533,15 +2634,14 @@
           <t>7501033961557</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2554,30 +2654,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>55</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1886326-800-auto?v=639109368905500000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-max-60-meq-con-zinc-fresa-139174/p</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2604,15 +2708,14 @@
           <t>7501033957369</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2625,30 +2728,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>47</v>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1881930-800-auto?v=639108181458370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-de-rehidratacion-pedialyte-max-60-manzana-91343/p</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2675,15 +2782,14 @@
           <t>7501033961540</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2696,30 +2802,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>41</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1886328-800-auto?v=639109369190430000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-max-60-coco-139175/p</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2746,15 +2856,14 @@
           <t>7501033959967</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2767,30 +2876,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>46</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1923862-800-auto?v=639139976717600000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-cereza-115207/p</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2817,15 +2930,14 @@
           <t>7501033957413</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2838,30 +2950,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>45</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1923712-800-auto?v=639139960218870000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-45-fresa-91344/p</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2888,15 +3004,14 @@
           <t>7501033959974</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2909,30 +3024,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>44</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1930910-800-auto?v=639147672423300000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-coco-115209/p</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2959,15 +3078,14 @@
           <t>7501033959950</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2980,30 +3098,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>47</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1883355-800-auto?v=639108424319730000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-manzana-115206/p</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3030,15 +3152,14 @@
           <t>7501033959981</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3051,30 +3172,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>47</v>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1883360-800-auto?v=639108424935200000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-durazno-115208/p</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3101,15 +3226,14 @@
           <t>7501033962394</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3122,30 +3246,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>47</v>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1888333-800-auto?v=639110047304100000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-45-guarana-148796/p</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3172,15 +3300,14 @@
           <t>8886451012074</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3193,34 +3320,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>6</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>27</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>156</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1664246-800-auto?v=638909591039200000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-peptigro-vainilla-156888/p</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3247,15 +3379,14 @@
           <t>8886451007049</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3268,34 +3399,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>6</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>24</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>156</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1940743-800-auto?v=639162591961230000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-vainilla-150499/p</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3322,15 +3458,14 @@
           <t>8886451012043</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3343,34 +3478,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>6</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>24</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>156</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1940743-800-auto?v=639162591961230000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-vainilla-150499/p</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3397,15 +3537,14 @@
           <t>8710428020185</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3418,34 +3557,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>6</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>26</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>156</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1889012-800-auto?v=639110162763330000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-rpb-vainilla-150857/p</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3472,15 +3616,14 @@
           <t>8710428020314</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3493,34 +3636,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>6</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>23</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>156</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1889006-800-auto?v=639110162367970000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-rpb-fresa-150855/p</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3547,15 +3695,14 @@
           <t>8886451012036</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3568,34 +3715,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>6</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>24</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>156</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1664234-800-auto?v=638909590254870000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-peptigro-fresa-156885/p</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3622,15 +3774,14 @@
           <t>8710428021885</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3643,30 +3794,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>28</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1782169-800-auto?v=638998339830370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-10-vainilla-polvo-157328/p</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3693,15 +3848,14 @@
           <t>8886451012029</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3714,34 +3868,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>24</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>156</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1757046-800-auto?v=638962121295800000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-peptigro-fresa-157240/p</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3768,15 +3927,14 @@
           <t>7703186799036</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3789,30 +3947,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>60</v>
       </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1963830-800-auto?v=639228058807430000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/oferta-pediasure-peptigro-vainilla-gratis-1-botella-x-220-ml-156951/p</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3839,15 +4001,14 @@
           <t>7703186033130</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3860,34 +4021,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>6</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>50</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>156</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890125-800-auto?v=639110367558830000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-rpb-vaini-pack-x-6-unds-154604/p</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3914,15 +4080,14 @@
           <t>7703186123480</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3935,30 +4100,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>45</v>
       </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1963829-800-auto?v=639228058620500000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/oferta-pediasure-peptigro-liquido-dscto-20-156949/p</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3985,15 +4154,14 @@
           <t>8710428024039</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4006,30 +4174,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>30</v>
       </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1816159-800-auto?v=639045005340070000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/pediasure-10-vainilla-liquido-157448/p</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4056,15 +4228,14 @@
           <t>5099864016987</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4077,30 +4248,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J50" t="n">
-        <v>0</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>33</v>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890131-800-auto?v=639110367951870000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/similac-1-formula-infantil-5-hmos-154605/p</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4127,15 +4302,14 @@
           <t>5099864016994</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4148,30 +4322,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>32</v>
       </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890066-800-auto?v=639110359442900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-1-5hmos-154560/p</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4198,15 +4376,14 @@
           <t>7703186863072</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4219,30 +4396,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J52" t="n">
-        <v>0</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>32</v>
       </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890132-800-auto?v=639110368216330000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/similac-1-formula-infantil-5-hmo-154606/p</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4269,15 +4450,14 @@
           <t>5099864017021</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4290,30 +4470,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>31</v>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890143-800-auto?v=639110370684600000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/leche-de-formula-en-polvo-similac-2-a-partir-de-6-meses-154619/p</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4340,15 +4524,14 @@
           <t>7703186502186</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4361,30 +4544,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J54" t="n">
-        <v>0</v>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>31</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890144-800-auto?v=639110370946970000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/leche-de-formula-en-polvo-similac-2-a-partir-de-6-meses-154620/p</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4411,15 +4598,14 @@
           <t>5099864017014</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4432,30 +4618,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J55" t="n">
-        <v>0</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>31</v>
       </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1889974-800-auto?v=639110345356730000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-2-5hmo-154476/p</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4482,15 +4672,14 @@
           <t>5099864017007</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4503,30 +4692,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J56" t="n">
-        <v>0</v>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>32</v>
       </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890001-800-auto?v=639110350559370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-2-5hmos-154502/p</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4553,15 +4746,14 @@
           <t>5099864017229</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4574,34 +4766,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
         <v>6</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>38</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>240</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Similac® 3 Kid es un alimento lácteo en polvo para niños desde los 2 años, con una fórmula científicamente diseñada que incluye grasas de fácil digestión, 5 HMOs (Oligosacáridos), nucleótidos, probiótico, prebióticos, DHA, hierro y luteína.</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1890086-800-auto?v=639110361671930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-de-crecimiento-similac-3-5hmos-154568/p</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4628,15 +4825,14 @@
           <t>5099864017212</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4649,34 +4845,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>6</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>38</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>240</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Similac® 3 Kid es un alimento lácteo en polvo para niños desde los 2 años, con una fórmula científicamente diseñada que incluye grasas de fácil digestión, 5 HMOs (Oligosacáridos), nucleótidos, probiótico, prebióticos, DHA, hierro y luteína.</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1924325-800-auto?v=639140026502370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-de-crecimiento-similac-3-5hmos-154569/p</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4703,15 +4904,14 @@
           <t>5099864017205</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4724,34 +4924,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>6</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>38</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>240</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Similac® 3 Kid es un alimento lácteo en polvo para niños desde los 2 años, con una fórmula científicamente diseñada que incluye grasas de fácil digestión, 5 HMOs (Oligosacáridos), nucleótidos, probiótico, prebióticos, DHA, hierro y luteína.</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1968887-800-auto?v=639245322338830000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-de-crecimiento-similac-3-5hmos-154420/p</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4768,21 +4973,19 @@
           <t>La Rebaja</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t>8427030005003</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4795,8 +4998,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J60" t="n">
-        <v>0</v>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -4807,14 +5012,15 @@
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/similac-ar-iq-plus-21240/p</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -4831,21 +5037,19 @@
           <t>La Rebaja</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>8427030004938</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4858,8 +5062,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J61" t="n">
-        <v>0</v>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -4870,14 +5076,15 @@
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-ar-iq-plus-21241/p</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -4904,15 +5111,14 @@
           <t>7703186029508</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4925,30 +5131,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J62" t="n">
-        <v>0</v>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>12</v>
       </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1877797-800-auto?v=639107492293530000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/similac-mama-19106/p</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4975,15 +5185,14 @@
           <t>7703186032836</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4996,30 +5205,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J63" t="n">
-        <v>0</v>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>51</v>
       </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr">
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1963740-800-auto?v=639228048321130000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/oferta-similac-mama-400-gr-pack-x-2-precio-especial-130239/p</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5046,15 +5259,14 @@
           <t>8427030003658</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5067,30 +5279,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J64" t="n">
-        <v>0</v>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>32</v>
       </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr">
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1947776-800-auto?v=639187421643900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-neosure-92345/p</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5117,15 +5333,14 @@
           <t>5099864017236</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5138,30 +5353,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J65" t="n">
-        <v>0</v>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>29</v>
       </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1967361-800-auto?v=639240197055900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-rice-154307/p</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5188,15 +5407,14 @@
           <t>8427030003238</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5209,30 +5427,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>36</v>
       </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1878327-800-auto?v=639107584865130000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-sin-lactosa-25542/p</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5259,15 +5481,14 @@
           <t>7703186032355</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5280,37 +5501,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J67" t="n">
-        <v>0</v>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>44</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1884498-800-auto?v=639109028152930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/formula-infantil-similac-total-comfort-1-hmo-121333/p</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q67"/>
+  <autoFilter ref="A1:R67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>